--- a/forms/trg/Formulir_TRG_imppd.xlsx
+++ b/forms/trg/Formulir_TRG_imppd.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B21)</f>
+        <f>COUNTA(Anggota!B5:B22)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F21)</f>
+        <f>COUNTA(Anggota!F5:F22)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Junaid, S.P, M.P, Ph.D</t>
+          <t>Prof. Ir. Andi Nasruddin, M.Sc, Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Instansi xxxxx</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Plant patology | Plant-microbe Interaction IoT for Plant Protection</t>
+          <t>Biological Control, Population Dynamics, Insect, Insect Ecology, Integrated Pest Management, Plant Protection; Instansi xxxxx</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -950,20 +946,24 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Sri Nur Aminah</t>
+          <t>Muhammad Junaid, S.P, M.P, Ph.D</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n"/>
+          <t>Instansi xxxxx</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Plant patology | Plant-microbe Interaction IoT for Plant Protection</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
@@ -983,24 +983,20 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Keith F. A. Walters, BSc, PhD, ARCS, FRSB, CBiol, FRES</t>
+          <t>Sri Nur Aminah</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Instansi xxxxx</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>Invertebrate Biology and Pest Management</t>
-        </is>
-      </c>
+          <t>Universitas Hasanuddin</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n"/>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
@@ -1020,12 +1016,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>jdsbfhdsbfkdhsbf</t>
+          <t>Prof. Keith F. A. Walters, BSc, PhD, ARCS, FRSB, CBiol, FRES</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1035,7 +1031,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>/Focus</t>
+          <t>Invertebrate Biology and Pest Management</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1057,12 +1053,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Sri Wahyuni Manwan</t>
+          <t>jdsbfhdsbfkdhsbf</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1072,7 +1068,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Nano-silica for controlling B. tabaci and pepper yellow leaf curl Indonesia virus on chili plants</t>
+          <t>/Focus</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1081,11 +1077,7 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>55180183900</t>
-        </is>
-      </c>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1096,18 +1088,42 @@
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Sri Wahyuni Manwan</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Instansi xxxxx</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Nano-silica for controlling B. tabaci and pepper yellow leaf curl Indonesia virus on chili plants</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57217150937</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1296,15 +1312,32 @@
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="12" t="n"/>
     </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
